--- a/agenda.xlsx
+++ b/agenda.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t xml:space="preserve">data</t>
   </si>
@@ -62,6 +62,15 @@
   </si>
   <si>
     <t xml:space="preserve">Inicio Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06-dez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aniversario do Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julia</t>
   </si>
 </sst>
 </file>
@@ -139,24 +148,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -352,105 +365,115 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="39.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="39.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44911</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>0.729166666666667</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44911</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44911</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>0.791666666666667</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>0.569444444444444</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
